--- a/Bom details.xlsx
+++ b/Bom details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ngw11000658\Downloads\TEST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ngw11000658\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40CB479-F028-471C-BBAE-50AB50130014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97488B41-065E-42FD-878E-FCE738D11AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{B3962CAF-7EBD-4156-AD70-194724843227}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1150,7 +1153,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1158,7 +1161,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5414,39 +5417,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -5479,9 +5482,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -5514,6 +5534,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -5575,13 +5612,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -5590,6 +5620,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -5654,18 +5691,38 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FE543E0-BCCA-4F7D-A8E9-5F3C1CA1C0DA}">
   <dimension ref="A1:E290"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/Bom details.xlsx
+++ b/Bom details.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ngw11000658\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97488B41-065E-42FD-878E-FCE738D11AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A4AAA1-85EC-4480-A6C8-B40F93D56040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{B3962CAF-7EBD-4156-AD70-194724843227}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="315">
   <si>
     <t>Sr No</t>
   </si>
@@ -62,27 +62,18 @@
     <t>54425027A</t>
   </si>
   <si>
-    <t>544254640124</t>
-  </si>
-  <si>
     <t>54420000PTD003</t>
   </si>
   <si>
     <t>54428126A</t>
   </si>
   <si>
-    <t>544254630831</t>
-  </si>
-  <si>
     <t>54420000PTP025</t>
   </si>
   <si>
     <t>54429826A</t>
   </si>
   <si>
-    <t>544254630819</t>
-  </si>
-  <si>
     <t>54420000PTP020</t>
   </si>
   <si>
@@ -92,15 +83,9 @@
     <t>54420528A</t>
   </si>
   <si>
-    <t>544254630874</t>
-  </si>
-  <si>
     <t>54420227A</t>
   </si>
   <si>
-    <t>544254630827</t>
-  </si>
-  <si>
     <t>54420000PTP034</t>
   </si>
   <si>
@@ -122,9 +107,6 @@
     <t>54424627A</t>
   </si>
   <si>
-    <t>544254640129</t>
-  </si>
-  <si>
     <t>54424327A</t>
   </si>
   <si>
@@ -143,9 +125,6 @@
     <t>54425227A</t>
   </si>
   <si>
-    <t>544254630825</t>
-  </si>
-  <si>
     <t>54425127A</t>
   </si>
   <si>
@@ -167,9 +146,6 @@
     <t>54857924A</t>
   </si>
   <si>
-    <t>544554610502</t>
-  </si>
-  <si>
     <t>54850000PTP001</t>
   </si>
   <si>
@@ -269,30 +245,18 @@
     <t>54732027A</t>
   </si>
   <si>
-    <t>547354600258</t>
-  </si>
-  <si>
     <t>547380400103</t>
   </si>
   <si>
     <t>54732427A</t>
   </si>
   <si>
-    <t>547354600124</t>
-  </si>
-  <si>
     <t>54733127A</t>
   </si>
   <si>
-    <t>547354600173</t>
-  </si>
-  <si>
     <t>54734327A</t>
   </si>
   <si>
-    <t>547354600104</t>
-  </si>
-  <si>
     <t>54738227A</t>
   </si>
   <si>
@@ -329,90 +293,51 @@
     <t>54650427A</t>
   </si>
   <si>
-    <t>546554610329</t>
-  </si>
-  <si>
     <t>572900000120</t>
   </si>
   <si>
     <t>54658927A</t>
   </si>
   <si>
-    <t>546554610324</t>
-  </si>
-  <si>
     <t>54659027A</t>
   </si>
   <si>
-    <t>546554610327</t>
-  </si>
-  <si>
     <t>572900000118</t>
   </si>
   <si>
     <t>54659127A</t>
   </si>
   <si>
-    <t>546554610317</t>
-  </si>
-  <si>
     <t>54659227A</t>
   </si>
   <si>
-    <t>546554610319</t>
-  </si>
-  <si>
     <t>54651327A</t>
   </si>
   <si>
-    <t>546554610321</t>
-  </si>
-  <si>
     <t>54651427A</t>
   </si>
   <si>
-    <t>546554610322</t>
-  </si>
-  <si>
     <t>54653527A</t>
   </si>
   <si>
-    <t>546554610323</t>
-  </si>
-  <si>
     <t>54653627A</t>
   </si>
   <si>
-    <t>546554610326</t>
-  </si>
-  <si>
     <t>54654127A</t>
   </si>
   <si>
-    <t>546554610318</t>
-  </si>
-  <si>
     <t>54654227A</t>
   </si>
   <si>
-    <t>546554610320</t>
-  </si>
-  <si>
     <t>54651227A</t>
   </si>
   <si>
-    <t>546554610328</t>
-  </si>
-  <si>
     <t>54658627A</t>
   </si>
   <si>
     <t>54655227A</t>
   </si>
   <si>
-    <t>546554610325</t>
-  </si>
-  <si>
     <t>54661327A</t>
   </si>
   <si>
@@ -422,15 +347,9 @@
     <t>54664127A</t>
   </si>
   <si>
-    <t>546654600361</t>
-  </si>
-  <si>
     <t>54664227A</t>
   </si>
   <si>
-    <t>546654600360</t>
-  </si>
-  <si>
     <t>54663527A</t>
   </si>
   <si>
@@ -455,90 +374,51 @@
     <t>54789027A</t>
   </si>
   <si>
-    <t>547854600122</t>
-  </si>
-  <si>
     <t>54780000PTP002</t>
   </si>
   <si>
     <t>54783027A</t>
   </si>
   <si>
-    <t>547854600120</t>
-  </si>
-  <si>
     <t>54782927A</t>
   </si>
   <si>
-    <t>547854600176</t>
-  </si>
-  <si>
     <t>54780000PTP001</t>
   </si>
   <si>
     <t>54781427A</t>
   </si>
   <si>
-    <t>547854600152</t>
-  </si>
-  <si>
     <t>54781327A</t>
   </si>
   <si>
-    <t>547854600174</t>
-  </si>
-  <si>
     <t>54783627A</t>
   </si>
   <si>
-    <t>547854600121</t>
-  </si>
-  <si>
     <t>54784227A</t>
   </si>
   <si>
-    <t>547854600118</t>
-  </si>
-  <si>
     <t>54784127A</t>
   </si>
   <si>
-    <t>547854600175</t>
-  </si>
-  <si>
     <t>54788927A</t>
   </si>
   <si>
-    <t>547854600178</t>
-  </si>
-  <si>
     <t>54783527A</t>
   </si>
   <si>
-    <t>547854600177</t>
-  </si>
-  <si>
     <t>54780427A</t>
   </si>
   <si>
-    <t>547854600171</t>
-  </si>
-  <si>
     <t>54791827A</t>
   </si>
   <si>
     <t>54794127A</t>
   </si>
   <si>
-    <t>547854600173</t>
-  </si>
-  <si>
     <t>54794227A</t>
   </si>
   <si>
-    <t>547854600172</t>
-  </si>
-  <si>
     <t>54791427A</t>
   </si>
   <si>
@@ -563,27 +443,15 @@
     <t>56041327A</t>
   </si>
   <si>
-    <t>548654600141</t>
-  </si>
-  <si>
     <t>56043627A</t>
   </si>
   <si>
-    <t>548654600149</t>
-  </si>
-  <si>
     <t>56043527A</t>
   </si>
   <si>
-    <t>548654600145</t>
-  </si>
-  <si>
     <t>56041427A</t>
   </si>
   <si>
-    <t>548654600142</t>
-  </si>
-  <si>
     <t>56048927A</t>
   </si>
   <si>
@@ -593,27 +461,15 @@
     <t>56049127A</t>
   </si>
   <si>
-    <t>548654600144</t>
-  </si>
-  <si>
     <t>56049227A</t>
   </si>
   <si>
-    <t>548654600148</t>
-  </si>
-  <si>
     <t>56044127A</t>
   </si>
   <si>
-    <t>548654600140</t>
-  </si>
-  <si>
     <t>56044227A</t>
   </si>
   <si>
-    <t>548654600139</t>
-  </si>
-  <si>
     <t>56051327A</t>
   </si>
   <si>
@@ -635,18 +491,12 @@
     <t>56059227A</t>
   </si>
   <si>
-    <t>548654600147</t>
-  </si>
-  <si>
     <t>56053627A</t>
   </si>
   <si>
     <t>56059127A</t>
   </si>
   <si>
-    <t>548654600143</t>
-  </si>
-  <si>
     <t>56053527A</t>
   </si>
   <si>
@@ -854,9 +704,6 @@
     <t>54785027A</t>
   </si>
   <si>
-    <t>547854600210</t>
-  </si>
-  <si>
     <t>54782027A</t>
   </si>
   <si>
@@ -867,9 +714,6 @@
   </si>
   <si>
     <t>54784727A</t>
-  </si>
-  <si>
-    <t>547854600209</t>
   </si>
   <si>
     <t>54784827A</t>
@@ -1149,7 +993,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1180,6 +1024,11 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1248,10 +1097,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1286,9 +1136,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{FF04A29C-4958-48B0-8C61-4E6FCC355966}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1345,12 +1197,12 @@
       <sheetData sheetId="4">
         <row r="29">
           <cell r="D29" t="str">
-            <v>56059227A</v>
+            <v>54792627A</v>
           </cell>
         </row>
         <row r="30">
           <cell r="D30" t="str">
-            <v>56059427A</v>
+            <v>54795027A</v>
           </cell>
         </row>
       </sheetData>
@@ -2234,8 +2086,8 @@
           <cell r="B63" t="str">
             <v>54735527A</v>
           </cell>
-          <cell r="C63" t="str">
-            <v>'547354600260</v>
+          <cell r="C63">
+            <v>547354600260</v>
           </cell>
           <cell r="D63">
             <v>547354600114</v>
@@ -2248,8 +2100,8 @@
           <cell r="B64" t="str">
             <v>54734127A</v>
           </cell>
-          <cell r="C64" t="str">
-            <v>'547354600260</v>
+          <cell r="C64">
+            <v>547354600260</v>
           </cell>
           <cell r="D64">
             <v>547354600114</v>
@@ -5317,6 +5169,7 @@
           <cell r="C283">
             <v>549754610175</v>
           </cell>
+          <cell r="D283"/>
           <cell r="E283" t="str">
             <v>54970000PTP002</v>
           </cell>
@@ -5328,6 +5181,7 @@
           <cell r="C284">
             <v>549754600133</v>
           </cell>
+          <cell r="D284"/>
           <cell r="E284" t="str">
             <v>54850000PTP001</v>
           </cell>
@@ -5339,6 +5193,7 @@
           <cell r="C285">
             <v>549754600131</v>
           </cell>
+          <cell r="D285"/>
           <cell r="E285" t="str">
             <v>54850000PTP001</v>
           </cell>
@@ -5398,6 +5253,11 @@
           <cell r="E289" t="str">
             <v>572900000118</v>
           </cell>
+        </row>
+        <row r="290">
+          <cell r="C290"/>
+          <cell r="D290"/>
+          <cell r="E290"/>
         </row>
       </sheetData>
       <sheetData sheetId="13"/>
@@ -5727,7 +5587,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" style="13" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5755,14 +5616,14 @@
       <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>6</v>
+      <c r="C2" s="6">
+        <v>544254640124</v>
       </c>
       <c r="D2" s="6">
         <v>544254640202</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5770,16 +5631,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C3" s="6">
+        <v>544254630831</v>
       </c>
       <c r="D3" s="6">
         <v>544254630512</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5787,16 +5648,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="C4" s="6">
+        <v>544254630819</v>
       </c>
       <c r="D4" s="6">
         <v>544254630510</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5804,16 +5665,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="C5" s="6">
+        <v>544254630831</v>
       </c>
       <c r="D5" s="6">
         <v>544254640219</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5821,16 +5682,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="C6" s="6">
+        <v>544254630874</v>
       </c>
       <c r="D6" s="6">
         <v>544254630510</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5838,16 +5699,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>18</v>
+        <v>13</v>
+      </c>
+      <c r="C7" s="6">
+        <v>544254630827</v>
       </c>
       <c r="D7" s="6">
         <v>544254610241</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5855,7 +5716,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8" s="6">
         <v>544254640126</v>
@@ -5864,7 +5725,7 @@
         <v>544254640216</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5872,7 +5733,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C9" s="6">
         <v>544254640260</v>
@@ -5881,7 +5742,7 @@
         <v>544254640251</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5889,7 +5750,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C10" s="6">
         <v>544254640127</v>
@@ -5898,7 +5759,7 @@
         <v>544254640217</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5906,7 +5767,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C11" s="6">
         <v>544254640128</v>
@@ -5915,7 +5776,7 @@
         <v>544254640218</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5923,16 +5784,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="C12" s="6">
+        <v>544254640129</v>
       </c>
       <c r="D12" s="6">
         <v>544254640216</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5940,7 +5801,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C13" s="6">
         <v>544254640126</v>
@@ -5949,7 +5810,7 @@
         <v>544254640213</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5957,7 +5818,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C14" s="6">
         <v>544254640260</v>
@@ -5966,7 +5827,7 @@
         <v>544254640248</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5974,7 +5835,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C15" s="6">
         <v>544254640128</v>
@@ -5983,7 +5844,7 @@
         <v>544254640215</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5991,7 +5852,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C16" s="6">
         <v>544254630816</v>
@@ -6000,7 +5861,7 @@
         <v>544254640204</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -6008,7 +5869,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C17" s="6">
         <v>544254640257</v>
@@ -6017,7 +5878,7 @@
         <v>544254640241</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -6025,16 +5886,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="C18" s="6">
+        <v>544254630825</v>
       </c>
       <c r="D18" s="6">
         <v>544254640205</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -6042,7 +5903,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C19" s="6">
         <v>544254630816</v>
@@ -6051,7 +5912,7 @@
         <v>544254640202</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -6059,16 +5920,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="C20" s="6">
+        <v>544254630825</v>
       </c>
       <c r="D20" s="6">
         <v>544254640203</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -6076,7 +5937,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C21" s="6">
         <v>544254640257</v>
@@ -6085,7 +5946,7 @@
         <v>544254640267</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -6093,7 +5954,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C22" s="6">
         <v>544254630820</v>
@@ -6102,7 +5963,7 @@
         <v>544254640197</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -6110,7 +5971,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C23" s="6">
         <v>544254630823</v>
@@ -6119,7 +5980,7 @@
         <v>544254630871</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -6127,16 +5988,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>41</v>
+        <v>33</v>
+      </c>
+      <c r="C24" s="6">
+        <v>544554610502</v>
       </c>
       <c r="D24" s="6">
         <v>544554640104</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -6144,7 +6005,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C25" s="6">
         <v>549754600192</v>
@@ -6153,7 +6014,7 @@
         <v>549754600119</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -6161,7 +6022,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C26" s="6">
         <v>549754600193</v>
@@ -6170,7 +6031,7 @@
         <v>549754600120</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -6178,7 +6039,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C27" s="6">
         <v>549754600194</v>
@@ -6187,7 +6048,7 @@
         <v>549754600186</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -6195,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C28" s="6">
         <v>549754600392</v>
@@ -6204,7 +6065,7 @@
         <v>549754600188</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -6212,7 +6073,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C29" s="6">
         <v>549754600393</v>
@@ -6221,7 +6082,7 @@
         <v>549754600189</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -6229,7 +6090,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C30" s="6">
         <v>549754600130</v>
@@ -6238,7 +6099,7 @@
         <v>549754600102</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -6246,7 +6107,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C31" s="6">
         <v>549754600138</v>
@@ -6255,7 +6116,7 @@
         <v>549754600124</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -6263,7 +6124,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C32" s="6">
         <v>549754600130</v>
@@ -6272,7 +6133,7 @@
         <v>549754600104</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -6280,7 +6141,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C33" s="6">
         <v>549754600138</v>
@@ -6289,7 +6150,7 @@
         <v>549754600126</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -6297,7 +6158,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C34" s="6">
         <v>549754600131</v>
@@ -6306,7 +6167,7 @@
         <v>549754600106</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -6314,7 +6175,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C35" s="6">
         <v>549754600132</v>
@@ -6323,7 +6184,7 @@
         <v>549754600108</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -6331,7 +6192,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C36" s="6">
         <v>549754600139</v>
@@ -6340,7 +6201,7 @@
         <v>549754600173</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -6348,7 +6209,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C37" s="6">
         <v>549754600131</v>
@@ -6357,7 +6218,7 @@
         <v>549754600109</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -6365,7 +6226,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C38" s="6">
         <v>549754600132</v>
@@ -6374,7 +6235,7 @@
         <v>549754600110</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -6382,7 +6243,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C39" s="6">
         <v>549754600139</v>
@@ -6391,7 +6252,7 @@
         <v>549754600127</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -6399,7 +6260,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C40" s="6">
         <v>549754600133</v>
@@ -6408,7 +6269,7 @@
         <v>549754600111</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -6416,7 +6277,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C41" s="6">
         <v>549754600134</v>
@@ -6425,7 +6286,7 @@
         <v>549754600112</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -6433,7 +6294,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C42" s="6">
         <v>549754600190</v>
@@ -6442,7 +6303,7 @@
         <v>549754600180</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -6450,7 +6311,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C43" s="6">
         <v>549754600133</v>
@@ -6459,7 +6320,7 @@
         <v>549754600113</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -6467,7 +6328,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C44" s="6">
         <v>549754600190</v>
@@ -6476,7 +6337,7 @@
         <v>549754600128</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -6484,7 +6345,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C45" s="6">
         <v>549754610189</v>
@@ -6493,7 +6354,7 @@
         <v>549754610185</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -6501,7 +6362,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C46" s="6">
         <v>549754600238</v>
@@ -6510,7 +6371,7 @@
         <v>549754600227</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -6518,7 +6379,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C47" s="6">
         <v>549754600239</v>
@@ -6527,7 +6388,7 @@
         <v>549754600231</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -6535,7 +6396,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C48" s="6">
         <v>549754600239</v>
@@ -6544,7 +6405,7 @@
         <v>549754600233</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -6552,7 +6413,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C49" s="6">
         <v>549754610175</v>
@@ -6561,7 +6422,7 @@
         <v>549754610173</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -6569,7 +6430,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C50" s="6">
         <v>549754610191</v>
@@ -6578,7 +6439,7 @@
         <v>549754610188</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -6586,16 +6447,16 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>75</v>
+        <v>66</v>
+      </c>
+      <c r="C51" s="7">
+        <v>547354600258</v>
       </c>
       <c r="D51" s="6">
         <v>547354600113</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -6603,16 +6464,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>78</v>
+        <v>68</v>
+      </c>
+      <c r="C52" s="6">
+        <v>547354600124</v>
       </c>
       <c r="D52" s="6">
         <v>547354600108</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -6620,16 +6481,16 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>80</v>
+        <v>69</v>
+      </c>
+      <c r="C53" s="6">
+        <v>547354600173</v>
       </c>
       <c r="D53" s="6">
         <v>547354600105</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -6637,16 +6498,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>82</v>
+        <v>70</v>
+      </c>
+      <c r="C54" s="6">
+        <v>547354600104</v>
       </c>
       <c r="D54" s="6">
         <v>547354600194</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -6654,16 +6515,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
+      </c>
+      <c r="C55" s="6">
+        <v>547354600173</v>
       </c>
       <c r="D55" s="6">
         <v>547354600105</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -6671,16 +6532,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="C56" s="6">
+        <v>547354600124</v>
       </c>
       <c r="D56" s="6">
         <v>547354600109</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -6688,16 +6549,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="C57" s="7">
+        <v>547354600258</v>
       </c>
       <c r="D57" s="6">
         <v>547354600113</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -6705,16 +6566,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
+      </c>
+      <c r="C58" s="6">
+        <v>547354600124</v>
       </c>
       <c r="D58" s="6">
         <v>547354600108</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -6722,16 +6583,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
+      </c>
+      <c r="C59" s="6">
+        <v>547354600124</v>
       </c>
       <c r="D59" s="6">
         <v>547354600109</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -6739,16 +6600,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="C60" s="7">
+        <v>547354600258</v>
       </c>
       <c r="D60" s="6">
         <v>547354600113</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -6756,16 +6617,16 @@
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="C61" s="7">
+        <v>547354600258</v>
       </c>
       <c r="D61" s="6">
         <v>547354600113</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -6773,16 +6634,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
+      </c>
+      <c r="C62" s="6">
+        <v>547354600104</v>
       </c>
       <c r="D62" s="6">
         <v>547354600194</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -6790,16 +6651,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D63" s="6">
         <v>547354600114</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -6807,16 +6668,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D64" s="6">
         <v>547354600114</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -6824,16 +6685,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>95</v>
+        <v>82</v>
+      </c>
+      <c r="C65" s="6">
+        <v>546554610329</v>
       </c>
       <c r="D65" s="6">
         <v>546554600356</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -6841,16 +6702,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>98</v>
+        <v>84</v>
+      </c>
+      <c r="C66" s="6">
+        <v>546554610324</v>
       </c>
       <c r="D66" s="6">
         <v>546554600348</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -6858,16 +6719,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>100</v>
+        <v>85</v>
+      </c>
+      <c r="C67" s="6">
+        <v>546554610327</v>
       </c>
       <c r="D67" s="6">
         <v>546554600353</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -6875,16 +6736,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>103</v>
+        <v>87</v>
+      </c>
+      <c r="C68" s="6">
+        <v>546554610317</v>
       </c>
       <c r="D68" s="6">
         <v>546554610294</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -6892,16 +6753,16 @@
         <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>105</v>
+        <v>88</v>
+      </c>
+      <c r="C69" s="6">
+        <v>546554610319</v>
       </c>
       <c r="D69" s="6">
         <v>546554610295</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -6909,16 +6770,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>107</v>
+        <v>89</v>
+      </c>
+      <c r="C70" s="6">
+        <v>546554610321</v>
       </c>
       <c r="D70" s="6">
         <v>546554610260</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -6926,16 +6787,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>109</v>
+        <v>90</v>
+      </c>
+      <c r="C71" s="6">
+        <v>546554610322</v>
       </c>
       <c r="D71" s="6">
         <v>546554610261</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -6943,16 +6804,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>111</v>
+        <v>91</v>
+      </c>
+      <c r="C72" s="6">
+        <v>546554610323</v>
       </c>
       <c r="D72" s="6">
         <v>546554610275</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -6960,16 +6821,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>113</v>
+        <v>92</v>
+      </c>
+      <c r="C73" s="6">
+        <v>546554610326</v>
       </c>
       <c r="D73" s="6">
         <v>546554610276</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -6977,16 +6838,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>115</v>
+        <v>93</v>
+      </c>
+      <c r="C74" s="6">
+        <v>546554610318</v>
       </c>
       <c r="D74" s="6">
         <v>546554610270</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -6994,16 +6855,16 @@
         <v>74</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>117</v>
+        <v>94</v>
+      </c>
+      <c r="C75" s="6">
+        <v>546554610320</v>
       </c>
       <c r="D75" s="6">
         <v>546554610285</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -7011,16 +6872,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>119</v>
+        <v>95</v>
+      </c>
+      <c r="C76" s="6">
+        <v>546554610328</v>
       </c>
       <c r="D76" s="6">
         <v>546554600355</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -7028,16 +6889,16 @@
         <v>76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="C77" s="6">
+        <v>546554610327</v>
       </c>
       <c r="D77" s="6">
         <v>546554610289</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -7045,16 +6906,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>122</v>
+        <v>97</v>
+      </c>
+      <c r="C78" s="6">
+        <v>546554610325</v>
       </c>
       <c r="D78" s="6">
         <v>546554600284</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -7062,16 +6923,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>107</v>
+        <v>98</v>
+      </c>
+      <c r="C79" s="6">
+        <v>546554610321</v>
       </c>
       <c r="D79" s="6">
         <v>546654600326</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -7079,16 +6940,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>109</v>
+        <v>99</v>
+      </c>
+      <c r="C80" s="6">
+        <v>546554610322</v>
       </c>
       <c r="D80" s="6">
         <v>546654600327</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -7096,16 +6957,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>126</v>
+        <v>100</v>
+      </c>
+      <c r="C81" s="6">
+        <v>546654600361</v>
       </c>
       <c r="D81" s="6">
         <v>546654600332</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -7113,16 +6974,16 @@
         <v>81</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>128</v>
+        <v>101</v>
+      </c>
+      <c r="C82" s="6">
+        <v>546654600360</v>
       </c>
       <c r="D82" s="6">
         <v>546654600347</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -7130,16 +6991,16 @@
         <v>82</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>111</v>
+        <v>102</v>
+      </c>
+      <c r="C83" s="6">
+        <v>546554610323</v>
       </c>
       <c r="D83" s="6">
         <v>546654600335</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -7147,16 +7008,16 @@
         <v>83</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>113</v>
+        <v>103</v>
+      </c>
+      <c r="C84" s="6">
+        <v>546554610326</v>
       </c>
       <c r="D84" s="6">
         <v>546654600336</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -7164,16 +7025,16 @@
         <v>84</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>95</v>
+        <v>104</v>
+      </c>
+      <c r="C85" s="6">
+        <v>546554610329</v>
       </c>
       <c r="D85" s="6">
         <v>546654600270</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -7181,16 +7042,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>98</v>
+        <v>105</v>
+      </c>
+      <c r="C86" s="6">
+        <v>546554610324</v>
       </c>
       <c r="D86" s="6">
         <v>546654600261</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -7198,16 +7059,16 @@
         <v>86</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>100</v>
+        <v>106</v>
+      </c>
+      <c r="C87" s="6">
+        <v>546554610327</v>
       </c>
       <c r="D87" s="6">
         <v>546654600266</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -7215,16 +7076,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>98</v>
+        <v>107</v>
+      </c>
+      <c r="C88" s="6">
+        <v>546554610324</v>
       </c>
       <c r="D88" s="6">
         <v>546654600262</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -7232,16 +7093,16 @@
         <v>88</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="C89" s="6">
+        <v>546554610327</v>
       </c>
       <c r="D89" s="6">
         <v>546654600267</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -7249,16 +7110,16 @@
         <v>89</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>137</v>
+        <v>109</v>
+      </c>
+      <c r="C90" s="6">
+        <v>547854600122</v>
       </c>
       <c r="D90" s="6">
         <v>547854600111</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -7266,16 +7127,16 @@
         <v>90</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>140</v>
+        <v>111</v>
+      </c>
+      <c r="C91" s="6">
+        <v>547854600120</v>
       </c>
       <c r="D91" s="6">
         <v>547854600107</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -7283,16 +7144,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>142</v>
+        <v>112</v>
+      </c>
+      <c r="C92" s="6">
+        <v>547854600176</v>
       </c>
       <c r="D92" s="6">
         <v>547854600167</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -7300,16 +7161,16 @@
         <v>92</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>145</v>
+        <v>114</v>
+      </c>
+      <c r="C93" s="6">
+        <v>547854600152</v>
       </c>
       <c r="D93" s="6">
         <v>547854600148</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -7317,16 +7178,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>147</v>
+        <v>115</v>
+      </c>
+      <c r="C94" s="6">
+        <v>547854600174</v>
       </c>
       <c r="D94" s="6">
         <v>547854600164</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -7334,16 +7195,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>149</v>
+        <v>116</v>
+      </c>
+      <c r="C95" s="6">
+        <v>547854600121</v>
       </c>
       <c r="D95" s="6">
         <v>547854600109</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -7351,16 +7212,16 @@
         <v>95</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>151</v>
+        <v>117</v>
+      </c>
+      <c r="C96" s="6">
+        <v>547854600118</v>
       </c>
       <c r="D96" s="6">
         <v>547854600105</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -7368,16 +7229,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>153</v>
+        <v>118</v>
+      </c>
+      <c r="C97" s="6">
+        <v>547854600175</v>
       </c>
       <c r="D97" s="6">
         <v>547854600166</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -7385,16 +7246,16 @@
         <v>97</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>155</v>
+        <v>119</v>
+      </c>
+      <c r="C98" s="6">
+        <v>547854600178</v>
       </c>
       <c r="D98" s="6">
         <v>547854600169</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -7402,16 +7263,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>157</v>
+        <v>120</v>
+      </c>
+      <c r="C99" s="6">
+        <v>547854600177</v>
       </c>
       <c r="D99" s="6">
         <v>547854600168</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -7419,16 +7280,16 @@
         <v>99</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>159</v>
+        <v>121</v>
+      </c>
+      <c r="C100" s="6">
+        <v>547854600171</v>
       </c>
       <c r="D100" s="6">
         <v>547854600160</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -7436,16 +7297,16 @@
         <v>100</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>137</v>
+        <v>122</v>
+      </c>
+      <c r="C101" s="6">
+        <v>547854600122</v>
       </c>
       <c r="D101" s="6">
         <v>547954600110</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -7453,16 +7314,16 @@
         <v>101</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>162</v>
+        <v>123</v>
+      </c>
+      <c r="C102" s="6">
+        <v>547854600173</v>
       </c>
       <c r="D102" s="6">
         <v>547954600130</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -7470,16 +7331,16 @@
         <v>102</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>164</v>
+        <v>124</v>
+      </c>
+      <c r="C103" s="6">
+        <v>547854600172</v>
       </c>
       <c r="D103" s="6">
         <v>547954600107</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -7487,16 +7348,16 @@
         <v>103</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>145</v>
+        <v>125</v>
+      </c>
+      <c r="C104" s="6">
+        <v>547854600152</v>
       </c>
       <c r="D104" s="6">
         <v>547954600121</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -7504,16 +7365,16 @@
         <v>104</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>149</v>
+        <v>126</v>
+      </c>
+      <c r="C105" s="6">
+        <v>547854600121</v>
       </c>
       <c r="D105" s="6">
         <v>547954600108</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -7521,16 +7382,16 @@
         <v>105</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>147</v>
+        <v>127</v>
+      </c>
+      <c r="C106" s="6">
+        <v>547854600174</v>
       </c>
       <c r="D106" s="6">
         <v>547954600127</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -7538,16 +7399,16 @@
         <v>106</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>155</v>
+        <v>128</v>
+      </c>
+      <c r="C107" s="6">
+        <v>547854600178</v>
       </c>
       <c r="D107" s="6">
         <v>547954600132</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -7555,16 +7416,16 @@
         <v>107</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>157</v>
+        <v>129</v>
+      </c>
+      <c r="C108" s="6">
+        <v>547854600177</v>
       </c>
       <c r="D108" s="6">
         <v>547954600131</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -7572,16 +7433,16 @@
         <v>108</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>159</v>
+        <v>130</v>
+      </c>
+      <c r="C109" s="6">
+        <v>547854600171</v>
       </c>
       <c r="D109" s="6">
         <v>547954600123</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -7589,16 +7450,16 @@
         <v>109</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
+      </c>
+      <c r="C110" s="6">
+        <v>547854600122</v>
       </c>
       <c r="D110" s="6">
         <v>547954600116</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -7606,16 +7467,16 @@
         <v>110</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>173</v>
+        <v>132</v>
+      </c>
+      <c r="C111" s="6">
+        <v>548654600141</v>
       </c>
       <c r="D111" s="6">
         <v>549054600107</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -7623,16 +7484,16 @@
         <v>111</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>175</v>
+        <v>133</v>
+      </c>
+      <c r="C112" s="6">
+        <v>548654600149</v>
       </c>
       <c r="D112" s="6">
         <v>549054600116</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -7640,16 +7501,16 @@
         <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>177</v>
+        <v>134</v>
+      </c>
+      <c r="C113" s="6">
+        <v>548654600145</v>
       </c>
       <c r="D113" s="6">
         <v>549054600112</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -7657,16 +7518,16 @@
         <v>113</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>179</v>
+        <v>135</v>
+      </c>
+      <c r="C114" s="6">
+        <v>548654600142</v>
       </c>
       <c r="D114" s="6">
         <v>549054600108</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -7674,7 +7535,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="C115" s="6">
         <v>548654600312</v>
@@ -7683,7 +7544,7 @@
         <v>549054600113</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -7691,7 +7552,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>181</v>
+        <v>137</v>
       </c>
       <c r="C116" s="6">
         <v>548654600313</v>
@@ -7700,7 +7561,7 @@
         <v>549054600117</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -7708,16 +7569,16 @@
         <v>116</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>183</v>
+        <v>138</v>
+      </c>
+      <c r="C117" s="6">
+        <v>548654600144</v>
       </c>
       <c r="D117" s="6">
         <v>549054600111</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -7725,16 +7586,16 @@
         <v>117</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>185</v>
+        <v>139</v>
+      </c>
+      <c r="C118" s="6">
+        <v>548654600148</v>
       </c>
       <c r="D118" s="6">
         <v>549054600115</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -7742,16 +7603,16 @@
         <v>118</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>187</v>
+        <v>140</v>
+      </c>
+      <c r="C119" s="6">
+        <v>548654600140</v>
       </c>
       <c r="D119" s="6">
         <v>549054600109</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -7759,16 +7620,16 @@
         <v>119</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>189</v>
+        <v>141</v>
+      </c>
+      <c r="C120" s="6">
+        <v>548654600139</v>
       </c>
       <c r="D120" s="6">
         <v>549054600106</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -7776,16 +7637,16 @@
         <v>120</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>173</v>
+        <v>142</v>
+      </c>
+      <c r="C121" s="6">
+        <v>548654600141</v>
       </c>
       <c r="D121" s="6">
         <v>548654600107</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -7793,16 +7654,16 @@
         <v>121</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>179</v>
+        <v>143</v>
+      </c>
+      <c r="C122" s="6">
+        <v>548654600142</v>
       </c>
       <c r="D122" s="6">
         <v>548654600108</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -7810,7 +7671,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="C123" s="6">
         <v>548654600312</v>
@@ -7819,7 +7680,7 @@
         <v>548654600113</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -7827,7 +7688,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="C124" s="6">
         <v>548654600313</v>
@@ -7836,7 +7697,7 @@
         <v>548654600118</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -7844,7 +7705,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="C125" s="6">
         <v>548654600312</v>
@@ -7853,7 +7714,7 @@
         <v>548654600114</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -7861,7 +7722,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>195</v>
+        <v>147</v>
       </c>
       <c r="C126" s="6">
         <v>548654600313</v>
@@ -7870,7 +7731,7 @@
         <v>548654600119</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -7878,16 +7739,16 @@
         <v>126</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>197</v>
+        <v>148</v>
+      </c>
+      <c r="C127" s="6">
+        <v>548654600147</v>
       </c>
       <c r="D127" s="6">
         <v>548654600106</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -7895,16 +7756,16 @@
         <v>127</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>175</v>
+        <v>149</v>
+      </c>
+      <c r="C128" s="6">
+        <v>548654600149</v>
       </c>
       <c r="D128" s="6">
         <v>548654600117</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -7912,16 +7773,16 @@
         <v>128</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>200</v>
+        <v>150</v>
+      </c>
+      <c r="C129" s="6">
+        <v>548654600143</v>
       </c>
       <c r="D129" s="6">
         <v>548654600109</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -7929,16 +7790,16 @@
         <v>129</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C130" s="6" t="s">
-        <v>177</v>
+        <v>151</v>
+      </c>
+      <c r="C130" s="6">
+        <v>548654600145</v>
       </c>
       <c r="D130" s="6">
         <v>548654600112</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -7946,7 +7807,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="C131" s="6">
         <v>546854620381</v>
@@ -7955,7 +7816,7 @@
         <v>546854650101</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -7963,7 +7824,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>204</v>
+        <v>154</v>
       </c>
       <c r="C132" s="6">
         <v>546854620382</v>
@@ -7972,7 +7833,7 @@
         <v>546854650102</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -7980,7 +7841,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="C133" s="6">
         <v>546854620355</v>
@@ -7989,7 +7850,7 @@
         <v>546854650110</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -7997,7 +7858,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="C134" s="6">
         <v>546854620387</v>
@@ -8006,7 +7867,7 @@
         <v>546854650111</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -8014,7 +7875,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="C135" s="6">
         <v>546854620346</v>
@@ -8023,7 +7884,7 @@
         <v>546854650115</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -8031,7 +7892,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>208</v>
+        <v>158</v>
       </c>
       <c r="C136" s="6">
         <v>546854620389</v>
@@ -8040,7 +7901,7 @@
         <v>546854650116</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -8048,7 +7909,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="C137" s="6">
         <v>0</v>
@@ -8057,7 +7918,7 @@
         <v>0</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -8065,7 +7926,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="C138" s="6">
         <v>0</v>
@@ -8074,7 +7935,7 @@
         <v>0</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -8082,7 +7943,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="C139" s="6">
         <v>0</v>
@@ -8091,7 +7952,7 @@
         <v>0</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -8099,7 +7960,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>213</v>
+        <v>163</v>
       </c>
       <c r="C140" s="6">
         <v>0</v>
@@ -8108,7 +7969,7 @@
         <v>0</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -8116,7 +7977,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="C141" s="6">
         <v>0</v>
@@ -8125,7 +7986,7 @@
         <v>0</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -8133,7 +7994,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="C142" s="6">
         <v>0</v>
@@ -8142,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -8150,7 +8011,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="C143" s="6">
         <v>0</v>
@@ -8159,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -8167,7 +8028,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="C144" s="6">
         <v>549754600194</v>
@@ -8176,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -8184,7 +8045,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>218</v>
+        <v>168</v>
       </c>
       <c r="C145" s="6">
         <v>549754600241</v>
@@ -8193,7 +8054,7 @@
         <v>0</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -8201,7 +8062,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="C146" s="6">
         <v>549754600223</v>
@@ -8210,7 +8071,7 @@
         <v>549754600119</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>220</v>
+        <v>170</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -8218,7 +8079,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="C147" s="6">
         <v>0</v>
@@ -8227,7 +8088,7 @@
         <v>0</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -8235,7 +8096,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>222</v>
+        <v>172</v>
       </c>
       <c r="C148" s="6">
         <v>549754600394</v>
@@ -8244,7 +8105,7 @@
         <v>549754600188</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>220</v>
+        <v>170</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -8252,16 +8113,16 @@
         <v>148</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C149" s="7" t="s">
-        <v>75</v>
+        <v>173</v>
+      </c>
+      <c r="C149" s="7">
+        <v>547354600258</v>
       </c>
       <c r="D149" s="6">
         <v>547354600107</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -8269,7 +8130,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="C150" s="6">
         <v>0</v>
@@ -8278,7 +8139,7 @@
         <v>547354600110</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -8286,16 +8147,16 @@
         <v>150</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C151" s="6" t="s">
-        <v>80</v>
+        <v>175</v>
+      </c>
+      <c r="C151" s="6">
+        <v>547354600173</v>
       </c>
       <c r="D151" s="6">
         <v>547354600105</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -8303,16 +8164,16 @@
         <v>151</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>82</v>
+        <v>176</v>
+      </c>
+      <c r="C152" s="6">
+        <v>547354600104</v>
       </c>
       <c r="D152" s="6">
         <v>547354600194</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -8320,16 +8181,16 @@
         <v>152</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>82</v>
+        <v>177</v>
+      </c>
+      <c r="C153" s="6">
+        <v>547354600104</v>
       </c>
       <c r="D153" s="6">
         <v>547354600194</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -8337,16 +8198,16 @@
         <v>153</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C154" s="6" t="s">
-        <v>80</v>
+        <v>178</v>
+      </c>
+      <c r="C154" s="6">
+        <v>547354600173</v>
       </c>
       <c r="D154" s="6">
         <v>547354600105</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -8354,16 +8215,16 @@
         <v>154</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>80</v>
+        <v>179</v>
+      </c>
+      <c r="C155" s="6">
+        <v>547354600173</v>
       </c>
       <c r="D155" s="6">
         <v>547354600105</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -8371,16 +8232,16 @@
         <v>155</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>98</v>
+        <v>180</v>
+      </c>
+      <c r="C156" s="6">
+        <v>546554610324</v>
       </c>
       <c r="D156" s="6">
         <v>546554600348</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -8388,16 +8249,16 @@
         <v>156</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>100</v>
+        <v>181</v>
+      </c>
+      <c r="C157" s="6">
+        <v>546554610327</v>
       </c>
       <c r="D157" s="6">
         <v>546554600353</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -8405,16 +8266,16 @@
         <v>157</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C158" s="6" t="s">
-        <v>98</v>
+        <v>182</v>
+      </c>
+      <c r="C158" s="6">
+        <v>546554610324</v>
       </c>
       <c r="D158" s="6">
         <v>546554600348</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -8422,16 +8283,16 @@
         <v>158</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>100</v>
+        <v>183</v>
+      </c>
+      <c r="C159" s="6">
+        <v>546554610327</v>
       </c>
       <c r="D159" s="6">
         <v>546554600353</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -8439,16 +8300,16 @@
         <v>159</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C160" s="6" t="s">
-        <v>98</v>
+        <v>184</v>
+      </c>
+      <c r="C160" s="6">
+        <v>546554610324</v>
       </c>
       <c r="D160" s="6">
         <v>546554600348</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -8456,16 +8317,16 @@
         <v>160</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C161" s="6" t="s">
-        <v>100</v>
+        <v>185</v>
+      </c>
+      <c r="C161" s="6">
+        <v>546554610327</v>
       </c>
       <c r="D161" s="6">
         <v>546554600353</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -8473,16 +8334,16 @@
         <v>161</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C162" s="6" t="s">
-        <v>103</v>
+        <v>186</v>
+      </c>
+      <c r="C162" s="6">
+        <v>546554610317</v>
       </c>
       <c r="D162" s="6">
         <v>546554610294</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -8490,16 +8351,16 @@
         <v>162</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C163" s="6" t="s">
-        <v>105</v>
+        <v>187</v>
+      </c>
+      <c r="C163" s="6">
+        <v>546554610319</v>
       </c>
       <c r="D163" s="6">
         <v>546554610295</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -8507,16 +8368,16 @@
         <v>163</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C164" s="6" t="s">
-        <v>107</v>
+        <v>188</v>
+      </c>
+      <c r="C164" s="6">
+        <v>546554610321</v>
       </c>
       <c r="D164" s="6">
         <v>546554610260</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -8524,16 +8385,16 @@
         <v>164</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C165" s="6" t="s">
-        <v>109</v>
+        <v>189</v>
+      </c>
+      <c r="C165" s="6">
+        <v>546554610322</v>
       </c>
       <c r="D165" s="6">
         <v>546554610261</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -8541,16 +8402,16 @@
         <v>165</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C166" s="6" t="s">
-        <v>111</v>
+        <v>190</v>
+      </c>
+      <c r="C166" s="6">
+        <v>546554610323</v>
       </c>
       <c r="D166" s="6">
         <v>546554610275</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -8558,16 +8419,16 @@
         <v>166</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>113</v>
+        <v>191</v>
+      </c>
+      <c r="C167" s="6">
+        <v>546554610326</v>
       </c>
       <c r="D167" s="6">
         <v>546554610276</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -8575,16 +8436,16 @@
         <v>167</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C168" s="6" t="s">
-        <v>115</v>
+        <v>192</v>
+      </c>
+      <c r="C168" s="6">
+        <v>546554610318</v>
       </c>
       <c r="D168" s="6">
         <v>546554610270</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -8592,16 +8453,16 @@
         <v>168</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C169" s="6" t="s">
-        <v>117</v>
+        <v>193</v>
+      </c>
+      <c r="C169" s="6">
+        <v>546554610320</v>
       </c>
       <c r="D169" s="6">
         <v>546554610285</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -8609,16 +8470,16 @@
         <v>169</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C170" s="6" t="s">
-        <v>98</v>
+        <v>194</v>
+      </c>
+      <c r="C170" s="6">
+        <v>546554610324</v>
       </c>
       <c r="D170" s="6">
         <v>546554600348</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -8626,7 +8487,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>245</v>
+        <v>195</v>
       </c>
       <c r="C171" s="6">
         <v>0</v>
@@ -8635,7 +8496,7 @@
         <v>546554600356</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -8643,16 +8504,16 @@
         <v>171</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C172" s="6" t="s">
-        <v>100</v>
+        <v>196</v>
+      </c>
+      <c r="C172" s="6">
+        <v>546554610327</v>
       </c>
       <c r="D172" s="6">
         <v>546554600353</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -8660,7 +8521,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>247</v>
+        <v>197</v>
       </c>
       <c r="C173" s="6">
         <v>549054600257</v>
@@ -8669,7 +8530,7 @@
         <v>549054600182</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -8677,16 +8538,16 @@
         <v>173</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C174" s="6" t="s">
-        <v>107</v>
+        <v>198</v>
+      </c>
+      <c r="C174" s="6">
+        <v>546554610321</v>
       </c>
       <c r="D174" s="6">
         <v>546654600326</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -8694,16 +8555,16 @@
         <v>174</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C175" s="6" t="s">
-        <v>109</v>
+        <v>199</v>
+      </c>
+      <c r="C175" s="6">
+        <v>546554610322</v>
       </c>
       <c r="D175" s="6">
         <v>546654600327</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -8711,16 +8572,16 @@
         <v>175</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C176" s="6" t="s">
-        <v>126</v>
+        <v>200</v>
+      </c>
+      <c r="C176" s="6">
+        <v>546654600361</v>
       </c>
       <c r="D176" s="6">
         <v>546654600332</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -8728,16 +8589,16 @@
         <v>176</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C177" s="6" t="s">
-        <v>128</v>
+        <v>201</v>
+      </c>
+      <c r="C177" s="6">
+        <v>546654600360</v>
       </c>
       <c r="D177" s="6">
         <v>546654600347</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -8745,16 +8606,16 @@
         <v>177</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C178" s="6" t="s">
-        <v>111</v>
+        <v>202</v>
+      </c>
+      <c r="C178" s="6">
+        <v>546554610323</v>
       </c>
       <c r="D178" s="6">
         <v>546654600335</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -8762,16 +8623,16 @@
         <v>178</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C179" s="6" t="s">
-        <v>113</v>
+        <v>203</v>
+      </c>
+      <c r="C179" s="6">
+        <v>546554610326</v>
       </c>
       <c r="D179" s="6">
         <v>546654600336</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -8779,16 +8640,16 @@
         <v>179</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C180" s="6" t="s">
-        <v>98</v>
+        <v>204</v>
+      </c>
+      <c r="C180" s="6">
+        <v>546554610324</v>
       </c>
       <c r="D180" s="6">
         <v>546654600261</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -8796,16 +8657,16 @@
         <v>180</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C181" s="6" t="s">
-        <v>100</v>
+        <v>205</v>
+      </c>
+      <c r="C181" s="6">
+        <v>546554610327</v>
       </c>
       <c r="D181" s="6">
         <v>546654600266</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -8813,16 +8674,16 @@
         <v>181</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C182" s="6" t="s">
-        <v>98</v>
+        <v>206</v>
+      </c>
+      <c r="C182" s="6">
+        <v>546554610324</v>
       </c>
       <c r="D182" s="6">
         <v>546654600262</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -8830,16 +8691,16 @@
         <v>182</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C183" s="6" t="s">
-        <v>100</v>
+        <v>207</v>
+      </c>
+      <c r="C183" s="6">
+        <v>546554610327</v>
       </c>
       <c r="D183" s="6">
         <v>546654600267</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -8847,16 +8708,16 @@
         <v>183</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C184" s="6" t="s">
-        <v>98</v>
+        <v>208</v>
+      </c>
+      <c r="C184" s="6">
+        <v>546554610324</v>
       </c>
       <c r="D184" s="6">
         <v>546654600261</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -8864,16 +8725,16 @@
         <v>184</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C185" s="6" t="s">
-        <v>100</v>
+        <v>209</v>
+      </c>
+      <c r="C185" s="6">
+        <v>546554610327</v>
       </c>
       <c r="D185" s="6">
         <v>546654600266</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -8881,16 +8742,16 @@
         <v>185</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C186" s="6" t="s">
-        <v>100</v>
+        <v>210</v>
+      </c>
+      <c r="C186" s="6">
+        <v>546554610327</v>
       </c>
       <c r="D186" s="6">
         <v>546654600267</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
@@ -8898,7 +8759,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>261</v>
+        <v>211</v>
       </c>
       <c r="C187" s="6">
         <v>549054600257</v>
@@ -8907,7 +8768,7 @@
         <v>548654600206</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -8915,7 +8776,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="C188" s="8">
         <v>549054600183</v>
@@ -8924,7 +8785,7 @@
         <v>548654600205</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
@@ -8932,7 +8793,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>263</v>
+        <v>213</v>
       </c>
       <c r="C189" s="6">
         <v>549054600257</v>
@@ -8941,7 +8802,7 @@
         <v>548654600207</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -8949,7 +8810,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="C190" s="6">
         <v>0</v>
@@ -8958,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -8966,16 +8827,16 @@
         <v>190</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C191" s="6" t="s">
-        <v>155</v>
+        <v>215</v>
+      </c>
+      <c r="C191" s="6">
+        <v>547854600178</v>
       </c>
       <c r="D191" s="6">
         <v>0</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -8983,16 +8844,16 @@
         <v>191</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C192" s="6" t="s">
-        <v>137</v>
+        <v>216</v>
+      </c>
+      <c r="C192" s="6">
+        <v>547854600122</v>
       </c>
       <c r="D192" s="6">
         <v>0</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -9000,7 +8861,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="C193" s="6">
         <v>0</v>
@@ -9009,7 +8870,7 @@
         <v>0</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -9017,7 +8878,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>268</v>
+        <v>218</v>
       </c>
       <c r="C194" s="6">
         <v>0</v>
@@ -9026,7 +8887,7 @@
         <v>547854600160</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
@@ -9034,16 +8895,16 @@
         <v>194</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C195" s="6" t="s">
-        <v>270</v>
+        <v>219</v>
+      </c>
+      <c r="C195" s="6">
+        <v>547854600210</v>
       </c>
       <c r="D195" s="6">
         <v>547854600208</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
@@ -9051,16 +8912,16 @@
         <v>195</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C196" s="6" t="s">
-        <v>137</v>
+        <v>220</v>
+      </c>
+      <c r="C196" s="6">
+        <v>547854600122</v>
       </c>
       <c r="D196" s="6">
         <v>547854600111</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -9068,16 +8929,16 @@
         <v>196</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C197" s="6" t="s">
-        <v>140</v>
+        <v>221</v>
+      </c>
+      <c r="C197" s="6">
+        <v>547854600120</v>
       </c>
       <c r="D197" s="6">
         <v>547854600107</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
@@ -9085,16 +8946,16 @@
         <v>197</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="C198" s="6" t="s">
-        <v>142</v>
+        <v>222</v>
+      </c>
+      <c r="C198" s="6">
+        <v>547854600176</v>
       </c>
       <c r="D198" s="6">
         <v>547854600167</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
@@ -9102,16 +8963,16 @@
         <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C199" s="6" t="s">
-        <v>275</v>
+        <v>223</v>
+      </c>
+      <c r="C199" s="6">
+        <v>547854600209</v>
       </c>
       <c r="D199" s="6">
         <v>547854600207</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -9119,16 +8980,16 @@
         <v>199</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C200" s="6" t="s">
-        <v>270</v>
+        <v>224</v>
+      </c>
+      <c r="C200" s="6">
+        <v>547854600210</v>
       </c>
       <c r="D200" s="6">
         <v>547854600208</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
@@ -9136,16 +8997,16 @@
         <v>200</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="C201" s="6" t="s">
-        <v>147</v>
+        <v>225</v>
+      </c>
+      <c r="C201" s="6">
+        <v>547854600174</v>
       </c>
       <c r="D201" s="6">
         <v>547854600164</v>
       </c>
       <c r="E201" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
@@ -9153,16 +9014,16 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="C202" s="6" t="s">
-        <v>145</v>
+        <v>226</v>
+      </c>
+      <c r="C202" s="6">
+        <v>547854600152</v>
       </c>
       <c r="D202" s="6">
         <v>547854600148</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -9170,16 +9031,16 @@
         <v>202</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="C203" s="6" t="s">
-        <v>155</v>
+        <v>227</v>
+      </c>
+      <c r="C203" s="6">
+        <v>547854600178</v>
       </c>
       <c r="D203" s="6">
         <v>547854600169</v>
       </c>
       <c r="E203" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
@@ -9187,16 +9048,16 @@
         <v>203</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="C204" s="6" t="s">
-        <v>275</v>
+        <v>228</v>
+      </c>
+      <c r="C204" s="6">
+        <v>547854600209</v>
       </c>
       <c r="D204" s="6">
         <v>547854600207</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -9204,16 +9065,16 @@
         <v>204</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C205" s="6" t="s">
-        <v>149</v>
+        <v>229</v>
+      </c>
+      <c r="C205" s="6">
+        <v>547854600121</v>
       </c>
       <c r="D205" s="6">
         <v>547854600109</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -9221,16 +9082,16 @@
         <v>205</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C206" s="6" t="s">
-        <v>153</v>
+        <v>230</v>
+      </c>
+      <c r="C206" s="6">
+        <v>547854600175</v>
       </c>
       <c r="D206" s="6">
         <v>547854600166</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -9238,16 +9099,16 @@
         <v>206</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C207" s="6" t="s">
-        <v>151</v>
+        <v>231</v>
+      </c>
+      <c r="C207" s="6">
+        <v>547854600118</v>
       </c>
       <c r="D207" s="6">
         <v>547854600105</v>
       </c>
       <c r="E207" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -9255,16 +9116,16 @@
         <v>207</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="C208" s="6" t="s">
-        <v>157</v>
+        <v>232</v>
+      </c>
+      <c r="C208" s="6">
+        <v>547854600177</v>
       </c>
       <c r="D208" s="6">
         <v>547854600168</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -9272,7 +9133,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>285</v>
+        <v>233</v>
       </c>
       <c r="C209" s="6">
         <v>0</v>
@@ -9281,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="E209" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -9289,7 +9150,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
       <c r="C210" s="6">
         <v>0</v>
@@ -9298,7 +9159,7 @@
         <v>547854600207</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -9306,16 +9167,16 @@
         <v>210</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C211" s="6" t="s">
-        <v>270</v>
+        <v>235</v>
+      </c>
+      <c r="C211" s="6">
+        <v>547854600210</v>
       </c>
       <c r="D211" s="6">
         <v>547854600208</v>
       </c>
       <c r="E211" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
@@ -9323,7 +9184,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>288</v>
+        <v>236</v>
       </c>
       <c r="C212" s="6">
         <v>0</v>
@@ -9332,7 +9193,7 @@
         <v>547854600207</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -9340,7 +9201,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>289</v>
+        <v>237</v>
       </c>
       <c r="C213" s="6">
         <v>0</v>
@@ -9349,7 +9210,7 @@
         <v>547854600208</v>
       </c>
       <c r="E213" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -9357,16 +9218,16 @@
         <v>213</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C214" s="6" t="s">
-        <v>155</v>
+        <v>238</v>
+      </c>
+      <c r="C214" s="6">
+        <v>547854600178</v>
       </c>
       <c r="D214" s="6">
         <v>0</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -9374,16 +9235,16 @@
         <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C215" s="6" t="s">
-        <v>137</v>
+        <v>239</v>
+      </c>
+      <c r="C215" s="6">
+        <v>547854600122</v>
       </c>
       <c r="D215" s="6">
         <v>0</v>
       </c>
       <c r="E215" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -9391,7 +9252,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>292</v>
+        <v>240</v>
       </c>
       <c r="C216" s="6">
         <v>0</v>
@@ -9400,7 +9261,7 @@
         <v>0</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -9408,16 +9269,16 @@
         <v>216</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C217" s="6" t="s">
-        <v>270</v>
+        <v>241</v>
+      </c>
+      <c r="C217" s="6">
+        <v>547854600210</v>
       </c>
       <c r="D217" s="6">
         <v>547954600144</v>
       </c>
       <c r="E217" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -9425,16 +9286,16 @@
         <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C218" s="6" t="s">
-        <v>137</v>
+        <v>242</v>
+      </c>
+      <c r="C218" s="6">
+        <v>547854600122</v>
       </c>
       <c r="D218" s="6">
         <v>547954600110</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -9442,16 +9303,16 @@
         <v>218</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C219" s="6" t="s">
-        <v>164</v>
+        <v>243</v>
+      </c>
+      <c r="C219" s="6">
+        <v>547854600172</v>
       </c>
       <c r="D219" s="6">
         <v>547954600107</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -9459,16 +9320,16 @@
         <v>219</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="C220" s="6" t="s">
-        <v>162</v>
+        <v>244</v>
+      </c>
+      <c r="C220" s="6">
+        <v>547854600173</v>
       </c>
       <c r="D220" s="6">
         <v>547954600130</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -9476,16 +9337,16 @@
         <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C221" s="6" t="s">
-        <v>149</v>
+        <v>245</v>
+      </c>
+      <c r="C221" s="6">
+        <v>547854600121</v>
       </c>
       <c r="D221" s="6">
         <v>547954600108</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -9493,16 +9354,16 @@
         <v>221</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C222" s="6" t="s">
-        <v>275</v>
+        <v>246</v>
+      </c>
+      <c r="C222" s="6">
+        <v>547854600209</v>
       </c>
       <c r="D222" s="6">
         <v>547954600142</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -9510,16 +9371,16 @@
         <v>222</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="C223" s="6" t="s">
-        <v>147</v>
+        <v>247</v>
+      </c>
+      <c r="C223" s="6">
+        <v>547854600174</v>
       </c>
       <c r="D223" s="6">
         <v>547954600127</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -9527,16 +9388,16 @@
         <v>223</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="C224" s="6" t="s">
-        <v>155</v>
+        <v>248</v>
+      </c>
+      <c r="C224" s="6">
+        <v>547854600178</v>
       </c>
       <c r="D224" s="6">
         <v>547954600132</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
@@ -9544,16 +9405,16 @@
         <v>224</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="C225" s="6" t="s">
-        <v>145</v>
+        <v>249</v>
+      </c>
+      <c r="C225" s="6">
+        <v>547854600152</v>
       </c>
       <c r="D225" s="6">
         <v>547954600121</v>
       </c>
       <c r="E225" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -9561,16 +9422,16 @@
         <v>225</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="C226" s="6" t="s">
-        <v>157</v>
+        <v>250</v>
+      </c>
+      <c r="C226" s="6">
+        <v>547854600177</v>
       </c>
       <c r="D226" s="6">
         <v>547954600131</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
@@ -9578,7 +9439,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>303</v>
+        <v>251</v>
       </c>
       <c r="C227" s="6">
         <v>0</v>
@@ -9587,7 +9448,7 @@
         <v>547954600133</v>
       </c>
       <c r="E227" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
@@ -9595,16 +9456,16 @@
         <v>227</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C228" s="6" t="s">
-        <v>270</v>
+        <v>252</v>
+      </c>
+      <c r="C228" s="6">
+        <v>547854600210</v>
       </c>
       <c r="D228" s="6">
         <v>547954600145</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -9612,7 +9473,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>305</v>
+        <v>253</v>
       </c>
       <c r="C229" s="6">
         <v>0</v>
@@ -9621,7 +9482,7 @@
         <v>547954600143</v>
       </c>
       <c r="E229" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -9629,16 +9490,16 @@
         <v>229</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="C230" s="6" t="s">
-        <v>137</v>
+        <v>254</v>
+      </c>
+      <c r="C230" s="6">
+        <v>547854600122</v>
       </c>
       <c r="D230" s="6">
         <v>547954600116</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -9646,7 +9507,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>307</v>
+        <v>255</v>
       </c>
       <c r="C231" s="6">
         <v>0</v>
@@ -9655,7 +9516,7 @@
         <v>547954600133</v>
       </c>
       <c r="E231" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -9663,16 +9524,16 @@
         <v>231</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C232" s="6" t="s">
-        <v>275</v>
+        <v>256</v>
+      </c>
+      <c r="C232" s="6">
+        <v>547854600209</v>
       </c>
       <c r="D232" s="6">
         <v>547954600142</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
@@ -9680,16 +9541,16 @@
         <v>232</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="C233" s="6" t="s">
-        <v>270</v>
+        <v>257</v>
+      </c>
+      <c r="C233" s="6">
+        <v>547854600210</v>
       </c>
       <c r="D233" s="6">
         <v>547954600144</v>
       </c>
       <c r="E233" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -9697,16 +9558,16 @@
         <v>233</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="C234" s="6" t="s">
-        <v>275</v>
+        <v>258</v>
+      </c>
+      <c r="C234" s="6">
+        <v>547854600209</v>
       </c>
       <c r="D234" s="6">
         <v>547954600143</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -9714,16 +9575,16 @@
         <v>234</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="C235" s="6" t="s">
-        <v>270</v>
+        <v>259</v>
+      </c>
+      <c r="C235" s="6">
+        <v>547854600210</v>
       </c>
       <c r="D235" s="6">
         <v>0</v>
       </c>
       <c r="E235" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
@@ -9731,7 +9592,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>312</v>
+        <v>260</v>
       </c>
       <c r="C236" s="6">
         <v>0</v>
@@ -9748,7 +9609,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>313</v>
+        <v>261</v>
       </c>
       <c r="C237" s="6">
         <v>0</v>
@@ -9757,7 +9618,7 @@
         <v>547954600142</v>
       </c>
       <c r="E237" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
@@ -9765,7 +9626,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>314</v>
+        <v>262</v>
       </c>
       <c r="C238" s="6">
         <v>547854600210</v>
@@ -9774,7 +9635,7 @@
         <v>547954600144</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
@@ -9782,7 +9643,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>315</v>
+        <v>263</v>
       </c>
       <c r="C239" s="6">
         <v>0</v>
@@ -9791,7 +9652,7 @@
         <v>547954600143</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
@@ -9799,16 +9660,16 @@
         <v>239</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>316</v>
+        <v>264</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>317</v>
+        <v>265</v>
       </c>
       <c r="D240" s="6">
         <v>0</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
@@ -9816,7 +9677,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
       <c r="C241" s="6">
         <v>0</v>
@@ -9825,7 +9686,7 @@
         <v>547954600142</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
@@ -9833,16 +9694,16 @@
         <v>241</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>319</v>
+        <v>267</v>
       </c>
       <c r="C242" s="6">
-        <v>0</v>
+        <v>547854600210</v>
       </c>
       <c r="D242" s="6">
         <v>547954600144</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
@@ -9850,7 +9711,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>320</v>
+        <v>268</v>
       </c>
       <c r="C243" s="6">
         <v>0</v>
@@ -9859,7 +9720,7 @@
         <v>547954600143</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
@@ -9867,7 +9728,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>321</v>
+        <v>269</v>
       </c>
       <c r="C244" s="6">
         <v>0</v>
@@ -9876,7 +9737,7 @@
         <v>0</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
@@ -9884,16 +9745,16 @@
         <v>244</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="C245" s="6" t="s">
-        <v>179</v>
+        <v>270</v>
+      </c>
+      <c r="C245" s="6">
+        <v>548654600142</v>
       </c>
       <c r="D245" s="6">
         <v>549054600108</v>
       </c>
-      <c r="E245" s="6" t="s">
-        <v>101</v>
+      <c r="E245" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -9901,7 +9762,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>323</v>
+        <v>271</v>
       </c>
       <c r="C246" s="6">
         <v>548654600312</v>
@@ -9909,8 +9770,8 @@
       <c r="D246" s="6">
         <v>549054600113</v>
       </c>
-      <c r="E246" s="6" t="s">
-        <v>96</v>
+      <c r="E246" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -9918,7 +9779,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>324</v>
+        <v>272</v>
       </c>
       <c r="C247" s="6">
         <v>548654600313</v>
@@ -9926,8 +9787,8 @@
       <c r="D247" s="6">
         <v>549054600117</v>
       </c>
-      <c r="E247" s="6" t="s">
-        <v>101</v>
+      <c r="E247" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -9935,7 +9796,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>325</v>
+        <v>273</v>
       </c>
       <c r="C248" s="6">
         <v>548654600312</v>
@@ -9943,8 +9804,8 @@
       <c r="D248" s="6">
         <v>549054600113</v>
       </c>
-      <c r="E248" s="6" t="s">
-        <v>96</v>
+      <c r="E248" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
@@ -9952,7 +9813,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>326</v>
+        <v>274</v>
       </c>
       <c r="C249" s="6">
         <v>548654600313</v>
@@ -9960,8 +9821,8 @@
       <c r="D249" s="6">
         <v>549054600117</v>
       </c>
-      <c r="E249" s="6" t="s">
-        <v>101</v>
+      <c r="E249" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -9969,16 +9830,16 @@
         <v>249</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="C250" s="6" t="s">
-        <v>185</v>
+        <v>275</v>
+      </c>
+      <c r="C250" s="6">
+        <v>548654600148</v>
       </c>
       <c r="D250" s="6">
         <v>549054600115</v>
       </c>
-      <c r="E250" s="6" t="s">
-        <v>101</v>
+      <c r="E250" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -9986,7 +9847,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>328</v>
+        <v>276</v>
       </c>
       <c r="C251" s="7">
         <v>549054600183</v>
@@ -9994,8 +9855,8 @@
       <c r="D251" s="6">
         <v>549054600181</v>
       </c>
-      <c r="E251" s="6" t="s">
-        <v>96</v>
+      <c r="E251" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -10003,7 +9864,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>329</v>
+        <v>277</v>
       </c>
       <c r="C252" s="6">
         <v>549054600257</v>
@@ -10011,8 +9872,8 @@
       <c r="D252" s="6">
         <v>549054600182</v>
       </c>
-      <c r="E252" s="6" t="s">
-        <v>101</v>
+      <c r="E252" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
@@ -10020,7 +9881,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>330</v>
+        <v>278</v>
       </c>
       <c r="C253" s="7">
         <v>549054600183</v>
@@ -10028,8 +9889,8 @@
       <c r="D253" s="6">
         <v>549054600219</v>
       </c>
-      <c r="E253" s="6" t="s">
-        <v>96</v>
+      <c r="E253" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
@@ -10037,7 +9898,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>331</v>
+        <v>279</v>
       </c>
       <c r="C254" s="6">
         <v>549054600257</v>
@@ -10045,8 +9906,8 @@
       <c r="D254" s="6">
         <v>549054600216</v>
       </c>
-      <c r="E254" s="6" t="s">
-        <v>101</v>
+      <c r="E254" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -10054,16 +9915,16 @@
         <v>254</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="C255" s="6" t="s">
-        <v>173</v>
+        <v>280</v>
+      </c>
+      <c r="C255" s="6">
+        <v>548654600141</v>
       </c>
       <c r="D255" s="6">
         <v>549054600107</v>
       </c>
-      <c r="E255" s="6" t="s">
-        <v>96</v>
+      <c r="E255" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
@@ -10071,16 +9932,16 @@
         <v>255</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="C256" s="6" t="s">
-        <v>187</v>
+        <v>281</v>
+      </c>
+      <c r="C256" s="6">
+        <v>548654600140</v>
       </c>
       <c r="D256" s="6">
         <v>549054600109</v>
       </c>
-      <c r="E256" s="6" t="s">
-        <v>96</v>
+      <c r="E256" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -10088,16 +9949,16 @@
         <v>256</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="C257" s="6" t="s">
-        <v>189</v>
+        <v>282</v>
+      </c>
+      <c r="C257" s="6">
+        <v>548654600139</v>
       </c>
       <c r="D257" s="6">
         <v>549054600106</v>
       </c>
-      <c r="E257" s="6" t="s">
-        <v>101</v>
+      <c r="E257" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -10105,16 +9966,16 @@
         <v>257</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="C258" s="6" t="s">
-        <v>183</v>
+        <v>283</v>
+      </c>
+      <c r="C258" s="6">
+        <v>548654600144</v>
       </c>
       <c r="D258" s="6">
         <v>549054600111</v>
       </c>
-      <c r="E258" s="6" t="s">
-        <v>96</v>
+      <c r="E258" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
@@ -10122,16 +9983,16 @@
         <v>258</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="C259" s="6" t="s">
-        <v>177</v>
+        <v>284</v>
+      </c>
+      <c r="C259" s="6">
+        <v>548654600145</v>
       </c>
       <c r="D259" s="6">
         <v>549054600112</v>
       </c>
-      <c r="E259" s="6" t="s">
-        <v>96</v>
+      <c r="E259" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
@@ -10139,16 +10000,16 @@
         <v>259</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="C260" s="6" t="s">
-        <v>175</v>
+        <v>285</v>
+      </c>
+      <c r="C260" s="6">
+        <v>548654600149</v>
       </c>
       <c r="D260" s="6">
         <v>549054600116</v>
       </c>
-      <c r="E260" s="6" t="s">
-        <v>101</v>
+      <c r="E260" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
@@ -10156,7 +10017,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>338</v>
+        <v>286</v>
       </c>
       <c r="C261" s="6">
         <v>549054600257</v>
@@ -10164,8 +10025,8 @@
       <c r="D261" s="6">
         <v>549054600182</v>
       </c>
-      <c r="E261" s="6" t="s">
-        <v>101</v>
+      <c r="E261" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
@@ -10173,16 +10034,16 @@
         <v>261</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="C262" s="6" t="s">
-        <v>173</v>
+        <v>287</v>
+      </c>
+      <c r="C262" s="6">
+        <v>548654600141</v>
       </c>
       <c r="D262" s="6">
         <v>548654600107</v>
       </c>
-      <c r="E262" s="6" t="s">
-        <v>96</v>
+      <c r="E262" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
@@ -10190,7 +10051,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>340</v>
+        <v>288</v>
       </c>
       <c r="C263" s="6">
         <v>548654600312</v>
@@ -10198,8 +10059,8 @@
       <c r="D263" s="6">
         <v>548654600113</v>
       </c>
-      <c r="E263" s="6" t="s">
-        <v>96</v>
+      <c r="E263" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
@@ -10207,7 +10068,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>341</v>
+        <v>289</v>
       </c>
       <c r="C264" s="6">
         <v>548654600313</v>
@@ -10215,8 +10076,8 @@
       <c r="D264" s="6">
         <v>548654600118</v>
       </c>
-      <c r="E264" s="6" t="s">
-        <v>101</v>
+      <c r="E264" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -10224,7 +10085,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>342</v>
+        <v>290</v>
       </c>
       <c r="C265" s="6">
         <v>548654600312</v>
@@ -10232,8 +10093,8 @@
       <c r="D265" s="6">
         <v>548654600114</v>
       </c>
-      <c r="E265" s="6" t="s">
-        <v>96</v>
+      <c r="E265" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -10241,7 +10102,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>343</v>
+        <v>291</v>
       </c>
       <c r="C266" s="6">
         <v>548654600313</v>
@@ -10249,8 +10110,8 @@
       <c r="D266" s="6">
         <v>548654600119</v>
       </c>
-      <c r="E266" s="6" t="s">
-        <v>101</v>
+      <c r="E266" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
@@ -10258,16 +10119,16 @@
         <v>266</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="C267" s="6" t="s">
-        <v>200</v>
+        <v>292</v>
+      </c>
+      <c r="C267" s="6">
+        <v>548654600143</v>
       </c>
       <c r="D267" s="6">
         <v>548654600109</v>
       </c>
-      <c r="E267" s="6" t="s">
-        <v>96</v>
+      <c r="E267" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
@@ -10275,16 +10136,16 @@
         <v>267</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="C268" s="6" t="s">
-        <v>197</v>
+        <v>293</v>
+      </c>
+      <c r="C268" s="6">
+        <v>548654600147</v>
       </c>
       <c r="D268" s="6">
         <v>548654600106</v>
       </c>
-      <c r="E268" s="6" t="s">
-        <v>101</v>
+      <c r="E268" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
@@ -10292,7 +10153,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>346</v>
+        <v>294</v>
       </c>
       <c r="C269" s="7">
         <v>549054600183</v>
@@ -10300,8 +10161,8 @@
       <c r="D269" s="6">
         <v>548654600236</v>
       </c>
-      <c r="E269" s="6" t="s">
-        <v>96</v>
+      <c r="E269" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -10309,7 +10170,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="C270" s="6">
         <v>549054600257</v>
@@ -10317,8 +10178,8 @@
       <c r="D270" s="6">
         <v>548654600234</v>
       </c>
-      <c r="E270" s="6" t="s">
-        <v>101</v>
+      <c r="E270" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
@@ -10326,7 +10187,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>348</v>
+        <v>296</v>
       </c>
       <c r="C271" s="6">
         <v>549054600257</v>
@@ -10334,8 +10195,8 @@
       <c r="D271" s="6">
         <v>548654600234</v>
       </c>
-      <c r="E271" s="6" t="s">
-        <v>101</v>
+      <c r="E271" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
@@ -10343,7 +10204,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>349</v>
+        <v>297</v>
       </c>
       <c r="C272" s="6">
         <v>549054600257</v>
@@ -10351,8 +10212,8 @@
       <c r="D272" s="6">
         <v>548654600233</v>
       </c>
-      <c r="E272" s="6" t="s">
-        <v>101</v>
+      <c r="E272" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -10360,16 +10221,16 @@
         <v>272</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="C273" s="6" t="s">
-        <v>177</v>
+        <v>298</v>
+      </c>
+      <c r="C273" s="6">
+        <v>548654600145</v>
       </c>
       <c r="D273" s="6">
         <v>548654600112</v>
       </c>
-      <c r="E273" s="6" t="s">
-        <v>96</v>
+      <c r="E273" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
@@ -10377,16 +10238,16 @@
         <v>273</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="C274" s="6" t="s">
-        <v>175</v>
+        <v>299</v>
+      </c>
+      <c r="C274" s="6">
+        <v>548654600149</v>
       </c>
       <c r="D274" s="6">
         <v>548654600117</v>
       </c>
-      <c r="E274" s="6" t="s">
-        <v>101</v>
+      <c r="E274" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
@@ -10394,16 +10255,16 @@
         <v>274</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C275" s="6" t="s">
-        <v>179</v>
+        <v>300</v>
+      </c>
+      <c r="C275" s="6">
+        <v>548654600142</v>
       </c>
       <c r="D275" s="6">
         <v>548654600108</v>
       </c>
-      <c r="E275" s="6" t="s">
-        <v>101</v>
+      <c r="E275" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
@@ -10411,7 +10272,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>353</v>
+        <v>301</v>
       </c>
       <c r="C276" s="7">
         <v>549054600183</v>
@@ -10419,8 +10280,8 @@
       <c r="D276" s="6">
         <v>548654600236</v>
       </c>
-      <c r="E276" s="6" t="s">
-        <v>96</v>
+      <c r="E276" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -10428,7 +10289,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>354</v>
+        <v>302</v>
       </c>
       <c r="C277" s="7">
         <v>549054600183</v>
@@ -10436,8 +10297,8 @@
       <c r="D277" s="6">
         <v>548654600235</v>
       </c>
-      <c r="E277" s="6" t="s">
-        <v>96</v>
+      <c r="E277" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
@@ -10445,7 +10306,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>355</v>
+        <v>303</v>
       </c>
       <c r="C278" s="7">
         <v>549054600183</v>
@@ -10453,8 +10314,8 @@
       <c r="D278" s="6">
         <v>548654600235</v>
       </c>
-      <c r="E278" s="6" t="s">
-        <v>96</v>
+      <c r="E278" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
@@ -10462,7 +10323,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>356</v>
+        <v>304</v>
       </c>
       <c r="C279" s="6">
         <v>549054600257</v>
@@ -10470,8 +10331,8 @@
       <c r="D279" s="6">
         <v>548654600233</v>
       </c>
-      <c r="E279" s="6" t="s">
-        <v>101</v>
+      <c r="E279" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
@@ -10479,7 +10340,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>357</v>
+        <v>305</v>
       </c>
       <c r="C280" s="6">
         <v>549054600257</v>
@@ -10487,8 +10348,8 @@
       <c r="D280" s="6">
         <v>548654600206</v>
       </c>
-      <c r="E280" s="6" t="s">
-        <v>101</v>
+      <c r="E280" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
@@ -10496,7 +10357,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>358</v>
+        <v>306</v>
       </c>
       <c r="C281" s="7">
         <v>549054600183</v>
@@ -10504,8 +10365,8 @@
       <c r="D281" s="6">
         <v>548654600205</v>
       </c>
-      <c r="E281" s="6" t="s">
-        <v>96</v>
+      <c r="E281" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -10513,7 +10374,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>359</v>
+        <v>307</v>
       </c>
       <c r="C282" s="6">
         <v>549054600257</v>
@@ -10521,8 +10382,8 @@
       <c r="D282" s="6">
         <v>548654600207</v>
       </c>
-      <c r="E282" s="6" t="s">
-        <v>101</v>
+      <c r="E282" s="6">
+        <v>572900000118</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
@@ -10530,44 +10391,46 @@
         <v>282</v>
       </c>
       <c r="B283" s="9" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
       <c r="C283" s="6">
         <v>549754610175</v>
       </c>
       <c r="D283" s="6"/>
       <c r="E283" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="4">
         <v>283</v>
       </c>
       <c r="B284" s="9" t="s">
-        <v>361</v>
+        <v>309</v>
       </c>
       <c r="C284" s="6">
         <v>549754600133</v>
       </c>
-      <c r="D284" s="6"/>
+      <c r="D284" s="6">
+        <v>549754600111</v>
+      </c>
       <c r="E284" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
         <v>284</v>
       </c>
       <c r="B285" s="9" t="s">
-        <v>362</v>
+        <v>310</v>
       </c>
       <c r="C285" s="6">
         <v>549754600131</v>
       </c>
       <c r="D285" s="6"/>
       <c r="E285" s="6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
@@ -10575,7 +10438,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="9" t="s">
-        <v>363</v>
+        <v>311</v>
       </c>
       <c r="C286" s="10">
         <v>549054600183</v>
@@ -10583,8 +10446,8 @@
       <c r="D286" s="6">
         <v>548654600204</v>
       </c>
-      <c r="E286" s="6" t="s">
-        <v>96</v>
+      <c r="E286" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -10592,7 +10455,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="9" t="s">
-        <v>364</v>
+        <v>312</v>
       </c>
       <c r="C287" s="10">
         <v>549054600183</v>
@@ -10600,8 +10463,8 @@
       <c r="D287" s="6">
         <v>549054600181</v>
       </c>
-      <c r="E287" s="6" t="s">
-        <v>96</v>
+      <c r="E287" s="6">
+        <v>572900000120</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
@@ -10609,7 +10472,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="9" t="s">
-        <v>365</v>
+        <v>313</v>
       </c>
       <c r="C288" s="10">
         <v>549054600183</v>
@@ -10619,7 +10482,7 @@
       </c>
       <c r="E288" s="4" t="str">
         <f>IFERROR(VLOOKUP('[1]Paint Float'!D29,'[1]Part Number Master'!B:E,4,0),0)</f>
-        <v>572900000118</v>
+        <v>54780000PTP002</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
@@ -10627,7 +10490,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="11" t="s">
-        <v>366</v>
+        <v>314</v>
       </c>
       <c r="C289" s="12">
         <v>549054600183</v>
@@ -10637,11 +10500,11 @@
       </c>
       <c r="E289" s="4" t="str">
         <f>IFERROR(VLOOKUP('[1]Paint Float'!D30,'[1]Part Number Master'!B:E,4,0),0)</f>
-        <v>572900000118</v>
+        <v>54780000PTP002</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C290"/>
+      <c r="C290" s="14"/>
       <c r="D290"/>
       <c r="E290"/>
     </row>
